--- a/data/credit_bond_2026-09-02.xlsx
+++ b/data/credit_bond_2026-09-02.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8200</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -783,7 +783,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X3" s="3"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>1.88%~1.98%</t>
+        </is>
+      </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1003,7 +1007,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>2.73%~2.83%</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>AAA</t>

--- a/data/credit_bond_2026-09-02.xlsx
+++ b/data/credit_bond_2026-09-02.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-02" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-03" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -719,8 +719,12 @@
           <t>1.50 ~ 2.20</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>53.11</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.86</t>
@@ -753,7 +757,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 18.19</t>
+          <t>C- 17.05</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -921,7 +925,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>09-02 17:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -962,7 +966,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.8134</t>
+          <t>2.8118</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -977,7 +981,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 37.24</t>
+          <t>B- 35.94</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-02.xlsx
+++ b/data/credit_bond_2026-09-02.xlsx
@@ -947,8 +947,12 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>134.61</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2.81</t>

--- a/data/credit_bond_2026-09-02.xlsx
+++ b/data/credit_bond_2026-09-02.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-03" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-04" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 17.05</t>
+          <t>C- 17.72</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 35.94</t>
+          <t>B- 37.49</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-02.xlsx
+++ b/data/credit_bond_2026-09-02.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-04" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-07" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26国耀04</t>
+          <t>26珠华04</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -702,62 +702,64 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>245990.SH</t>
+          <t>520444.SZ</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>2+2+1</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F3" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>53.11</v>
+        <v>134.61</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>25国耀融汇MTN002</t>
+          <t>25珠华02</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2.04Y</t>
+          <t>2.21Y+2.00Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.8676</t>
+          <t>2.8118</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/1.8200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>国耀融汇融资租赁有限公司</t>
+          <t>珠海华发集团有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 17.72</t>
+          <t>B- 38.58</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -780,16 +782,18 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>2.3</v>
+      </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>2.73%~2.83%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -800,17 +804,17 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过6.00亿元用于偿还有息债务,剩余部分用于补充公司融资租赁业务、保理业务等日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出[24控租03]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于置换到期的公司债券本金[23珠华Y3]</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司</t>
+          <t>华金证券股份有限公司,国泰海通证券股份有限公司,西部证券股份有限公司,中信建投证券股份有限公司,光大证券股份有限公司,国信证券股份有限公司,中国银河证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
         </is>
       </c>
       <c r="AD3" s="3"/>
@@ -821,27 +825,27 @@
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>国耀融汇融资租赁有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>珠海华发集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK3" s="3"/>
@@ -862,37 +866,37 @@
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP3" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AV3" s="3" t="inlineStr">
@@ -902,7 +906,7 @@
       </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX3" s="3" t="inlineStr">
@@ -920,7 +924,7 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26珠华04</t>
+          <t>26国耀04</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -930,62 +934,64 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>520444.SZ</t>
+          <t>245990.SH</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2+2+1</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F4" s="3"/>
+        <v>8.0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>134.61</v>
+        <v>53.11</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>25珠华02</t>
+          <t>25国耀融汇MTN002</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.21Y+2.00Y</t>
+          <t>2.04Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.8118</t>
+          <t>1.8676</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8200</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司</t>
+          <t>国耀融汇融资租赁有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 37.49</t>
+          <t>C- 18.43</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1008,16 +1014,18 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>3.01</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>2.73%~2.83%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1028,17 +1036,17 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于置换到期的公司债券本金[23珠华Y3]</t>
+          <t>本期债券募集资金不超过6.00亿元用于偿还有息债务,剩余部分用于补充公司融资租赁业务、保理业务等日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出[24控租03]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>华金证券股份有限公司,国泰海通证券股份有限公司,西部证券股份有限公司,中信建投证券股份有限公司,光大证券股份有限公司,国信证券股份有限公司,中国银河证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
@@ -1049,27 +1057,27 @@
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>国耀融汇融资租赁有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
@@ -1090,37 +1098,37 @@
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AV4" s="3" t="inlineStr">
@@ -1130,7 +1138,7 @@
       </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-02.xlsx
+++ b/data/credit_bond_2026-09-02.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-07" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-08" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>B- 38.58</t>
+          <t>B- 38.69</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 18.43</t>
+          <t>C- 19.74</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
